--- a/TestData/ResetPassword_TestData.xlsx
+++ b/TestData/ResetPassword_TestData.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="ResetPassword" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -783,4 +784,114 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>UserName</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Password</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>FirstName</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>LastName</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Zip</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Successful Login using Email</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>lawma195.infinity@gmail.com</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="n">
+        <v>12345678</v>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>Kima</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>Tlau</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="n">
+        <v>796701</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Successful Login using Phone</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>855 965321152</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="n">
+        <v>12345678</v>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>Kima</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>Tlau</t>
+        </is>
+      </c>
+      <c r="F3" s="1" t="n">
+        <v>796701</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>